--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_grid_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_grid_pref.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -525,7 +525,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
         <v>9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
